--- a/excel/roleSkin.xlsx
+++ b/excel/roleSkin.xlsx
@@ -130,7 +130,7 @@
     <t>roleId</t>
   </si>
   <si>
-    <t>reward</t>
+    <t>name</t>
   </si>
   <si>
     <t>string</t>
@@ -344,6 +344,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -354,7 +355,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4105,7 +4105,6 @@
     </row>
     <row r="447" spans="1:4">
       <c r="A447" s="5"/>
-      <c r="B447" s="2"/>
       <c r="C447" s="5"/>
       <c r="D447" s="5"/>
     </row>

--- a/excel/roleSkin.xlsx
+++ b/excel/roleSkin.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12360"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">变卖物编号为300001-400000
+          <t xml:space="preserve">角色皮肤编号为300001-400000
 </t>
         </r>
       </text>
@@ -71,34 +71,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-0：普通类型</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-0：白
-1：绿
-2：蓝
-3：紫
-4：金
-5：红</t>
+对应角色表id</t>
         </r>
       </text>
     </comment>
@@ -344,13 +317,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
